--- a/data/trans_camb/IP1015-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Clase-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-3,82; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>-1,88; 0,0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>-1,68; 0,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 0,0</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-1,85; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,3</t>
+          <t>-0,54; 0,3</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,0</t>
+          <t>-1,66; 0,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,02</t>
+          <t>-1,66; 1,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,48</t>
+          <t>-0,97; 0,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,52</t>
+          <t>-0,96; 0,51</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1577,22 +1577,22 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,47</t>
+          <t>-0,51; 0,46</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,29</t>
+          <t>-0,61; 0,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,26</t>
+          <t>-0,25; 0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,16</t>
+          <t>-0,27; 0,15</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Clase-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,0</t>
+          <t>-4,63; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,0</t>
+          <t>-1,67; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,0</t>
+          <t>-1,5; 0,0</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,0</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,62</t>
+          <t>-1,08; 0,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,22</t>
+          <t>-0,69; 0,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,3</t>
+          <t>-0,65; 0,3</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,99</t>
+          <t>-1,67; 1,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,44</t>
+          <t>-1,69; 1,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,48</t>
+          <t>-0,98; 0,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,51</t>
+          <t>-1,07; 0,52</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 4,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1582,17 +1582,17 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,28</t>
+          <t>-0,7; 0,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 0,26</t>
+          <t>-0,22; 0,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,15</t>
+          <t>-0,31; 0,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1015-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,05; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,0</t>
+          <t>-1,68; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,0</t>
+          <t>-1,88; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,35</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,09; 0,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,22</t>
+          <t>-0,7; 0,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,3</t>
+          <t>-0,69; 0,3</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-11,64%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-11,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,06</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,05</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,66; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,65; 1,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,48</t>
+          <t>-1,19; 0,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,52</t>
+          <t>-1,21; 0,52</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-10,67%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-8,81%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-10,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-8,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>-0,51; 0,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,61; 0,29</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,46</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,27</t>
+          <t>-0,22; 0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,14</t>
+          <t>-0,28; 0,16</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-5,56%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-36,57%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-5,56%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-36,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
